--- a/tests/Unit/Service/Inventory/inventory-invalid-document-id.xlsx
+++ b/tests/Unit/Service/Inventory/inventory-invalid-document-id.xlsx
@@ -85,7 +85,7 @@
     <t>5034</t>
   </si>
   <si>
-    <t>5034-789</t>
+    <t>5034/789</t>
   </si>
   <si>
     <t>123-document-naam.pdf</t>
